--- a/result/train_info_resnet18_part_detrend_plr_stft_bin_win.xlsx
+++ b/result/train_info_resnet18_part_detrend_plr_stft_bin_win.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5197521659585732</v>
+        <v>0.5987412232523687</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3107856669016844</v>
+        <v>0.4182798754005037</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8712374581939799</v>
+        <v>0.802675585284281</v>
       </c>
       <c r="F2" t="n">
-        <v>0.874766355140187</v>
+        <v>0.7957339117859725</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8673091178650852</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8710217755443886</v>
+        <v>0.8056368960468521</v>
       </c>
       <c r="I2" t="n">
-        <v>54.28103470802307</v>
+        <v>42.81876158714294</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.209060869792706</v>
+        <v>0.3024799760159819</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.124698880624533</v>
+        <v>0.1643073774609693</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9516908212560387</v>
+        <v>0.9355258268301747</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9593067068575735</v>
+        <v>0.9437523593808984</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9436619718309859</v>
+        <v>0.9266123054114158</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9514200298953662</v>
+        <v>0.9351037965214138</v>
       </c>
       <c r="I3" t="n">
-        <v>54.88330316543579</v>
+        <v>43.4263768196106</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.09360542992527084</v>
+        <v>0.1362163068914861</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07335899395664283</v>
+        <v>0.09041678600189601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9734299516908212</v>
+        <v>0.966183574879227</v>
       </c>
       <c r="F4" t="n">
-        <v>0.974025974025974</v>
+        <v>0.9638643067846607</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9729429206819866</v>
+        <v>0.9688658265381764</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9734841461153347</v>
+        <v>0.9663585951940851</v>
       </c>
       <c r="I4" t="n">
-        <v>55.8114070892334</v>
+        <v>43.54556751251221</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.05289719144974241</v>
+        <v>0.07413826641567151</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05092530054131181</v>
+        <v>0.0537092073713071</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9821627647714605</v>
+        <v>0.9810479375696767</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9836431226765799</v>
+        <v>0.9916666666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9807264640474426</v>
+        <v>0.9703484062268347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9821826280623608</v>
+        <v>0.9808917197452229</v>
       </c>
       <c r="I5" t="n">
-        <v>56.34456944465637</v>
+        <v>43.28072762489319</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0414439832988364</v>
+        <v>0.04844525226983961</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07042655431870068</v>
+        <v>0.05976019767212913</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9782608695652174</v>
+        <v>0.9775176514306949</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9809914275065226</v>
+        <v>0.9784626810248793</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9755374351371386</v>
+        <v>0.9766493699036323</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9782568295855789</v>
+        <v>0.9775551845668707</v>
       </c>
       <c r="I6" t="n">
-        <v>56.46525883674622</v>
+        <v>46.18726754188538</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03665227071724346</v>
+        <v>0.03824216268278927</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06753428930178362</v>
+        <v>0.06888968993485327</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9773318468970643</v>
+        <v>0.9764028242289112</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9853051996985682</v>
+        <v>0.9856441254250095</v>
       </c>
       <c r="G7" t="n">
-        <v>0.969236471460341</v>
+        <v>0.9670126019273536</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9772047832585949</v>
+        <v>0.9762394761459308</v>
       </c>
       <c r="I7" t="n">
-        <v>57.29966902732849</v>
+        <v>45.05339002609253</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02680085663686567</v>
+        <v>0.02978305656911444</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02593913564832017</v>
+        <v>0.01937222230377657</v>
       </c>
       <c r="E8" t="n">
         <v>0.9929394277220365</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9907749077490775</v>
+        <v>0.9922279792746114</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9929733727810651</v>
+        <v>0.9929629629629629</v>
       </c>
       <c r="I8" t="n">
-        <v>58.46932172775269</v>
+        <v>45.40521049499512</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02221821544977423</v>
+        <v>0.02521662618597545</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03597622596918462</v>
+        <v>0.02468823274901394</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9882943143812709</v>
+        <v>0.9920104050538833</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9962335216572504</v>
+        <v>0.9878721058434399</v>
       </c>
       <c r="G9" t="n">
-        <v>0.980355819125278</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9882308985615542</v>
+        <v>0.9920649566340654</v>
       </c>
       <c r="I9" t="n">
-        <v>58.62575554847717</v>
+        <v>45.22772026062012</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02479332320271565</v>
+        <v>0.02045512939051057</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03032911708595689</v>
+        <v>0.04284285334129707</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9905239687848384</v>
+        <v>0.9853214418431809</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9936590824319284</v>
+        <v>0.9753176043557169</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9873980726464048</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9905186837702176</v>
+        <v>0.9855125618925362</v>
       </c>
       <c r="I10" t="n">
-        <v>59.09553909301758</v>
+        <v>45.82092642784119</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01743768143613254</v>
+        <v>0.02062978783870632</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03457011128107593</v>
+        <v>0.02662150099536524</v>
       </c>
       <c r="E11" t="n">
-        <v>0.987736900780379</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9906785980611484</v>
+        <v>0.9922193404964802</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9848035581912528</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H11" t="n">
-        <v>0.987732342007435</v>
+        <v>0.9924031869557162</v>
       </c>
       <c r="I11" t="n">
-        <v>59.50577878952026</v>
+        <v>47.13825058937073</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02024171257209706</v>
+        <v>0.01817696270961344</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03776005703755628</v>
+        <v>0.01599090371983361</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9886659234485321</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9874306839186692</v>
+        <v>0.9977636973537085</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H12" t="n">
-        <v>0.988709975939293</v>
+        <v>0.9949823452889798</v>
       </c>
       <c r="I12" t="n">
-        <v>59.91238641738892</v>
+        <v>49.6306574344635</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01427288847178764</v>
+        <v>0.01934373491549384</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01896087222296864</v>
+        <v>0.04417312568599171</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9933110367892977</v>
+        <v>0.9879227053140096</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9936943620178041</v>
+        <v>0.9831192660550458</v>
       </c>
       <c r="G13" t="n">
         <v>0.9929577464788732</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9933259176863182</v>
+        <v>0.9880140143831827</v>
       </c>
       <c r="I13" t="n">
-        <v>59.52318620681763</v>
+        <v>49.51612138748169</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01517202692010995</v>
+        <v>0.01381661921066601</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02342981174581315</v>
+        <v>0.01700028635837339</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9918246005202527</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9914814814814815</v>
+        <v>0.9959153360564427</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9922164566345441</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9918488329010745</v>
+        <v>0.994991652754591</v>
       </c>
       <c r="I14" t="n">
-        <v>60.71075916290283</v>
+        <v>48.93148875236511</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01760798700830319</v>
+        <v>0.01639111484088267</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02731621450108762</v>
+        <v>0.04162367248336631</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9901523597175771</v>
+        <v>0.986250464511334</v>
       </c>
       <c r="F15" t="n">
-        <v>0.986034546122749</v>
+        <v>0.9767441860465116</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9902195977117549</v>
+        <v>0.9864220183486239</v>
       </c>
       <c r="I15" t="n">
-        <v>60.72426128387451</v>
+        <v>50.19295859336853</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01226224996538841</v>
+        <v>0.01467031086535671</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02285575917088454</v>
+        <v>0.02789460010027524</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.990709773318469</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9918669131238448</v>
+        <v>0.9892830746489283</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9931519526189154</v>
+        <v>0.9907475943745374</v>
       </c>
       <c r="I16" t="n">
-        <v>60.49152851104736</v>
+        <v>50.07657909393311</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01296922656842811</v>
+        <v>0.0121643307494888</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03671936602823148</v>
+        <v>0.05067533337018251</v>
       </c>
       <c r="E17" t="n">
-        <v>0.990709773318469</v>
+        <v>0.986250464511334</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9839181286549707</v>
+        <v>0.9760522496371553</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9907986750092014</v>
+        <v>0.9864319765309865</v>
       </c>
       <c r="I17" t="n">
-        <v>59.1932806968689</v>
+        <v>48.92940640449524</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0148591344340394</v>
+        <v>0.0126765845253136</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02877888715269386</v>
+        <v>0.01693440780700419</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9918578830495929</v>
+        <v>0.9948148148148148</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9925925925925926</v>
+        <v>0.9951834012597258</v>
       </c>
       <c r="I18" t="n">
-        <v>59.09301042556763</v>
+        <v>47.52625250816345</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.009149287495263593</v>
+        <v>0.01185419379715956</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03807495644488112</v>
+        <v>0.02337041724511641</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9903381642512077</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9929210134128167</v>
+        <v>0.9958939902948861</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.9888806523350631</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9903381642512077</v>
+        <v>0.9923749302585084</v>
       </c>
       <c r="I19" t="n">
-        <v>58.51431226730347</v>
+        <v>49.92025661468506</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01207605278081081</v>
+        <v>0.009290267252764786</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02661607139289225</v>
+        <v>0.01443409180615566</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9927536231884058</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9922251018141429</v>
+        <v>0.9996261682242991</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9911045218680504</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9927764400814966</v>
+        <v>0.9953471058998697</v>
       </c>
       <c r="I20" t="n">
-        <v>58.41756772994995</v>
+        <v>50.22775912284851</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.009005484003863005</v>
+        <v>0.007325996733560881</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01768726137423546</v>
+        <v>0.01095540416803455</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.99702712746191</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9886280264123257</v>
+        <v>0.996299037749815</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9937315634218289</v>
+        <v>0.9970370370370371</v>
       </c>
       <c r="I21" t="n">
-        <v>59.03667902946472</v>
+        <v>49.43267035484314</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.00656906453716489</v>
+        <v>0.004356273398025966</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0187360131645113</v>
+        <v>0.01643319537157023</v>
       </c>
       <c r="E22" t="n">
         <v>0.9938684503901896</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9929707732149463</v>
+        <v>0.9977586850952559</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9938900203665988</v>
+        <v>0.9938604651162791</v>
       </c>
       <c r="I22" t="n">
-        <v>59.96792125701904</v>
+        <v>47.38767981529236</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.006029415511087545</v>
+        <v>0.01242139119707804</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0325190119725642</v>
+        <v>0.01449439980486059</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9903381642512077</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9892751479289941</v>
+        <v>0.9922594913380022</v>
       </c>
       <c r="G23" t="n">
-        <v>0.991475166790215</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H23" t="n">
-        <v>0.990373935579415</v>
+        <v>0.9950101644797634</v>
       </c>
       <c r="I23" t="n">
-        <v>60.08932256698608</v>
+        <v>42.91944146156311</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01103181225989545</v>
+        <v>0.008905966186151403</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02177811093947343</v>
+        <v>0.01386166414912079</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.9981378026070763</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9918458117123795</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9931341621822231</v>
+        <v>0.9957272896154561</v>
       </c>
       <c r="I24" t="n">
-        <v>60.29181504249573</v>
+        <v>40.23337817192078</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.009967152681820775</v>
+        <v>0.01114201105253399</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01534411955230066</v>
+        <v>0.01940380733096993</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9929863418235512</v>
+        <v>0.996276991809382</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9950064730904383</v>
+        <v>0.9940564635958395</v>
       </c>
       <c r="I25" t="n">
-        <v>60.49398565292358</v>
+        <v>39.2080283164978</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.004886452320996507</v>
+        <v>0.005529029850477405</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01828439688195958</v>
+        <v>0.006914211525398089</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9946116685247121</v>
+        <v>0.9979561501300632</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9904446894524072</v>
+        <v>0.9974083672713809</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9946484591252999</v>
+        <v>0.9979625856640119</v>
       </c>
       <c r="I26" t="n">
-        <v>60.26043176651001</v>
+        <v>39.35172390937805</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.005900214816911291</v>
+        <v>0.002384082215671491</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.02189303519210251</v>
+        <v>0.005291191694852209</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9962839093273876</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9951923076923077</v>
+        <v>0.9988864142538976</v>
       </c>
       <c r="G27" t="n">
         <v>0.997405485544848</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9962976675305443</v>
+        <v>0.9981454005934718</v>
       </c>
       <c r="I27" t="n">
-        <v>58.91526198387146</v>
+        <v>39.95471119880676</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.006358848468221824</v>
+        <v>0.005964627971551748</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01296411485434715</v>
+        <v>0.004743211792101755</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9973987365291713</v>
+        <v>0.9977703455964325</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9981440237564959</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9974035608308606</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="I28" t="n">
-        <v>58.10839009284973</v>
+        <v>42.21908497810364</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.006068070096418516</v>
+        <v>0.0001443594049313093</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03561194597164736</v>
+        <v>0.003683672586060556</v>
       </c>
       <c r="E29" t="n">
-        <v>0.990709773318469</v>
+        <v>0.998513563730955</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9853372434017595</v>
+        <v>0.9988872403560831</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9907851087357169</v>
+        <v>0.9985168705969596</v>
       </c>
       <c r="I29" t="n">
-        <v>57.65229535102844</v>
+        <v>39.5678825378418</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.005956769653662371</v>
+        <v>0.0152599175970156</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01206784509449003</v>
+        <v>0.01400074541715395</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9972129319955407</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F30" t="n">
-        <v>0.997773654916512</v>
+        <v>0.9966517857142857</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9972186167253848</v>
+        <v>0.9948013367991088</v>
       </c>
       <c r="I30" t="n">
-        <v>57.3572883605957</v>
+        <v>42.46910166740417</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.004197661535903747</v>
+        <v>0.005844657169423268</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03660316693792497</v>
+        <v>0.01967124394377068</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9890375325157934</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9940097341819544</v>
+        <v>0.9871653832049871</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9840622683469237</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9890109890109891</v>
+        <v>0.9924423963133641</v>
       </c>
       <c r="I31" t="n">
-        <v>57.34064912796021</v>
+        <v>43.57345199584961</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.004214472259765059</v>
+        <v>0.003091479927538082</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01162467117158017</v>
+        <v>0.006145308570900244</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9979561501300632</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9933603836222796</v>
+        <v>0.9992567818654775</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9957478276945831</v>
+        <v>0.9979588049730933</v>
       </c>
       <c r="I32" t="n">
-        <v>57.49044871330261</v>
+        <v>42.60214185714722</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.002956955135742912</v>
+        <v>0.006804427891254491</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00787387023138526</v>
+        <v>0.01185453750294121</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9975845410628019</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9970381340244354</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9975921466938322</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="I33" t="n">
-        <v>57.8855447769165</v>
+        <v>42.36786770820618</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.005057702482750664</v>
+        <v>0.005032650622333616</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02535249080991372</v>
+        <v>0.01648270394053784</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9936826458565589</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9918578830495929</v>
+        <v>0.9929681717246485</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9925925925925926</v>
+        <v>0.9937037037037038</v>
       </c>
       <c r="I34" t="n">
-        <v>58.45140719413757</v>
+        <v>42.30510139465332</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.006021159282932451</v>
+        <v>0.0044315342279958</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02186781267380512</v>
+        <v>0.0117363530786145</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9968413229282794</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9889746416758545</v>
+        <v>0.9988835132117603</v>
       </c>
       <c r="G35" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9931721719874516</v>
+        <v>0.9968430826369545</v>
       </c>
       <c r="I35" t="n">
-        <v>58.73328924179077</v>
+        <v>42.57405161857605</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.006154998808983954</v>
+        <v>0.004637835466830788</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01407163883409312</v>
+        <v>0.007018713680492736</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9962839093273876</v>
+        <v>0.9973987365291713</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9966691339748335</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9974074074074074</v>
       </c>
       <c r="I36" t="n">
-        <v>59.41949701309204</v>
+        <v>42.29310250282288</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.002178381661641798</v>
+        <v>0.0004104996318524868</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02301221430714745</v>
+        <v>0.004693695858210189</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9983277591973244</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9933333333333333</v>
+        <v>0.9992573338284441</v>
       </c>
       <c r="G37" t="n">
-        <v>0.994069681245367</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H37" t="n">
-        <v>0.993701370878103</v>
+        <v>0.998330550918197</v>
       </c>
       <c r="I37" t="n">
-        <v>59.46099925041199</v>
+        <v>42.39683651924133</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.001692637620751279</v>
+        <v>0.004591731721741925</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01245376893948294</v>
+        <v>0.0409029180880346</v>
       </c>
       <c r="E38" t="n">
-        <v>0.99702712746191</v>
+        <v>0.9873652917131178</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9966666666666667</v>
+        <v>0.9788783685360525</v>
       </c>
       <c r="G38" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9970359392367544</v>
+        <v>0.9875091844232182</v>
       </c>
       <c r="I38" t="n">
-        <v>59.36038637161255</v>
+        <v>42.16904044151306</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.003697515141739389</v>
+        <v>0.005379966265216551</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01138827949754003</v>
+        <v>0.006621293036392704</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9962839093273876</v>
+        <v>0.9979561501300632</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9944608567208272</v>
+        <v>0.9985157699443413</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9963004069552349</v>
+        <v>0.9979603189319488</v>
       </c>
       <c r="I39" t="n">
-        <v>58.61981463432312</v>
+        <v>41.92211866378784</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.001210422085873808</v>
+        <v>0.001456851460160346</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01039999708211108</v>
+        <v>0.00488449749080585</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9973987365291713</v>
+        <v>0.998513563730955</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9970370370370371</v>
+        <v>0.9988872403560831</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9974064468321601</v>
+        <v>0.9985168705969596</v>
       </c>
       <c r="I40" t="n">
-        <v>57.79926061630249</v>
+        <v>42.1247136592865</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3.750940775221737e-05</v>
+        <v>0.0001250815962995137</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.01126108520836913</v>
+        <v>0.006167445429304086</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9972129319955407</v>
+        <v>0.9979561501300632</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9959334565619223</v>
+        <v>0.997040325564188</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H41" t="n">
-        <v>0.997223764575236</v>
+        <v>0.9979633401221996</v>
       </c>
       <c r="I41" t="n">
-        <v>57.32728600502014</v>
+        <v>42.53134155273438</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>1.892899458247064e-05</v>
+        <v>4.64554267871039e-05</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01040581424449415</v>
+        <v>0.004515246756463953</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9975845410628019</v>
+        <v>0.9986993682645856</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9966703662597114</v>
+        <v>0.9992578849721707</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9975930383262359</v>
+        <v>0.9987020211385129</v>
       </c>
       <c r="I42" t="n">
-        <v>57.05382227897644</v>
+        <v>42.14215064048767</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1.090529772650191e-05</v>
+        <v>0.006479160224886516</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0101073976994201</v>
+        <v>0.01522891448235121</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9977703455964325</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F43" t="n">
-        <v>0.997039230199852</v>
+        <v>0.9937199852234947</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9977777777777778</v>
+        <v>0.9953746530989824</v>
       </c>
       <c r="I43" t="n">
-        <v>56.84227800369263</v>
+        <v>42.30255627632141</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>6.195894425282054e-06</v>
+        <v>0.003153250246413826</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01055578518169423</v>
+        <v>0.004627491801720438</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9977703455964325</v>
+        <v>0.9983277591973244</v>
       </c>
       <c r="F44" t="n">
-        <v>0.997039230199852</v>
+        <v>0.9992573338284441</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9977777777777778</v>
+        <v>0.998330550918197</v>
       </c>
       <c r="I44" t="n">
-        <v>56.85845828056335</v>
+        <v>42.43420743942261</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>5.416349343722719e-06</v>
+        <v>0.002628389471575054</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01014303813345587</v>
+        <v>0.0127970800789244</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9975845410628019</v>
+        <v>0.9959123002601263</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9970381340244354</v>
+        <v>0.9933628318584071</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9975921466938322</v>
+        <v>0.9959334565619223</v>
       </c>
       <c r="I45" t="n">
-        <v>57.94057583808899</v>
+        <v>42.54022526741028</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1.223681821174827e-05</v>
+        <v>0.003099239949783518</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01042936470244378</v>
+        <v>0.009484295776749837</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9975845410628019</v>
+        <v>0.9972129319955407</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9970381340244354</v>
+        <v>0.9988843436221644</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9975921466938322</v>
+        <v>0.9972155188416558</v>
       </c>
       <c r="I46" t="n">
-        <v>58.26893067359924</v>
+        <v>42.28939056396484</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.004408283507586513</v>
+        <v>0.002330879328790864</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.03942631089787093</v>
+        <v>0.01442253167635483</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9860646599777034</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9841269841269841</v>
+        <v>0.9992534527808884</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9881393624907339</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9861290919178842</v>
+        <v>0.995722521852334</v>
       </c>
       <c r="I47" t="n">
-        <v>58.55724835395813</v>
+        <v>42.61624646186829</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.008911322932689328</v>
+        <v>0.001764605700813794</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01151546531092429</v>
+        <v>0.01221453291601828</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9972129319955407</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9955604883462819</v>
+        <v>0.9996275605214152</v>
       </c>
       <c r="G48" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9964821329383448</v>
+        <v>0.9972134497492104</v>
       </c>
       <c r="I48" t="n">
-        <v>58.57192921638489</v>
+        <v>42.83882570266724</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.002100526950970592</v>
+        <v>0.001706861202289452</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01031485823274089</v>
+        <v>0.01083394414741632</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9973987365291713</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9944567627494457</v>
+        <v>0.9970370370370371</v>
       </c>
       <c r="G49" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9959289415247965</v>
+        <v>0.9974064468321601</v>
       </c>
       <c r="I49" t="n">
-        <v>59.1277015209198</v>
+        <v>42.91274189949036</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.002384382312778939</v>
+        <v>0.003216287846592075</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0146097341043606</v>
+        <v>0.005148839179931325</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9983277591973244</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9985096870342772</v>
+        <v>0.9988868274582561</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9983311700352309</v>
       </c>
       <c r="I50" t="n">
-        <v>59.02044749259949</v>
+        <v>42.69048118591309</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.001937428905071201</v>
+        <v>0.0001738759903518708</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01082989365205926</v>
+        <v>0.004071092162418874</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9975845410628019</v>
+        <v>0.998513563730955</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9977753058954394</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="G51" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9975903614457832</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="I51" t="n">
-        <v>58.3759298324585</v>
+        <v>42.58174443244934</v>
       </c>
     </row>
   </sheetData>
